--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -7847,7 +7847,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>personal role</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">

--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -7847,7 +7847,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>personal role</t>
+          <t>role</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
